--- a/output/yearly_benthic_cover_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_43_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.34824397799676</v>
+        <v>45.59528117768797</v>
       </c>
       <c r="M2" t="n">
-        <v>100.554200672301</v>
+        <v>99.18835417531764</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04677164807984</v>
+        <v>88.07729418420487</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93567461694222</v>
+        <v>45.93550090214011</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228775230688079</v>
+        <v>2.228853606003148</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711409392585945</v>
+        <v>5.713035333018638</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429250768960265</v>
+        <v>0.7429512020010495</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97534604615825</v>
+        <v>33.97495437118376</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17455353721721</v>
+        <v>34.17575529204827</v>
       </c>
       <c r="I3" t="n">
-        <v>6.570480633934149</v>
+        <v>6.598299367443448</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643281730600165</v>
+        <v>4.643445012506559</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95322835192016</v>
+        <v>11.92270581579513</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87525519142351</v>
+        <v>48.90496124070784</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7641581602859</v>
+        <v>106.7631679586431</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.14621996827368</v>
+        <v>87.13549538800527</v>
       </c>
       <c r="C4" t="n">
-        <v>42.67047082123521</v>
+        <v>42.63442618370748</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185467280706743</v>
+        <v>2.183367758091176</v>
       </c>
       <c r="E4" t="n">
-        <v>6.514911397844572</v>
+        <v>6.514807443394666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444842761362368</v>
+        <v>0.744517264837297</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31516166914894</v>
+        <v>33.28160259465543</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24627670226688</v>
+        <v>34.24779418251565</v>
       </c>
       <c r="I4" t="n">
-        <v>5.486891916318833</v>
+        <v>5.510173239277926</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653026725851479</v>
+        <v>4.653232905233106</v>
       </c>
       <c r="K4" t="n">
-        <v>12.85378003172632</v>
+        <v>12.86450461199473</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29323579609584</v>
+        <v>44.31778311075771</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81748664905737</v>
+        <v>99.81671390645991</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.94480676673489</v>
+        <v>86.02431116746617</v>
       </c>
       <c r="C5" t="n">
-        <v>42.32067974400861</v>
+        <v>42.37841267922806</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126746496286655</v>
+        <v>2.129363790049084</v>
       </c>
       <c r="E5" t="n">
-        <v>7.103286008135261</v>
+        <v>7.120334498775237</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458068826339441</v>
+        <v>0.7458443223250675</v>
       </c>
       <c r="G5" t="n">
-        <v>32.42002476018462</v>
+        <v>32.45840705361532</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30711660116142</v>
+        <v>34.3088388269531</v>
       </c>
       <c r="I5" t="n">
-        <v>4.580533001870828</v>
+        <v>4.599995661216676</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66129301646215</v>
+        <v>4.661527014531672</v>
       </c>
       <c r="K5" t="n">
-        <v>14.05519323326515</v>
+        <v>13.97568883253383</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47171335838405</v>
+        <v>43.49283812048036</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84758633565779</v>
+        <v>99.84693963224227</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.60672761512349</v>
+        <v>84.73387096884017</v>
       </c>
       <c r="C6" t="n">
-        <v>41.69397013477781</v>
+        <v>41.8023977524188</v>
       </c>
       <c r="D6" t="n">
-        <v>2.061521384692896</v>
+        <v>2.066598117542234</v>
       </c>
       <c r="E6" t="n">
-        <v>7.52257890189624</v>
+        <v>7.550306872400611</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469301641596922</v>
+        <v>0.7469707452155965</v>
       </c>
       <c r="G6" t="n">
-        <v>31.4257361900388</v>
+        <v>31.50165473316082</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35878755134583</v>
+        <v>34.36065427991743</v>
       </c>
       <c r="I6" t="n">
-        <v>3.822859896991951</v>
+        <v>3.839119063005979</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668313525998075</v>
+        <v>4.668567157597479</v>
       </c>
       <c r="K6" t="n">
-        <v>15.39327238487653</v>
+        <v>15.26612903115984</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78552045251593</v>
+        <v>42.80369555916533</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87276297217028</v>
+        <v>99.87222234274398</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.11003413418474</v>
+        <v>83.23838943742761</v>
       </c>
       <c r="C7" t="n">
-        <v>40.79102592331999</v>
+        <v>40.90325991787976</v>
       </c>
       <c r="D7" t="n">
-        <v>1.988825318938798</v>
+        <v>1.993990601423949</v>
       </c>
       <c r="E7" t="n">
-        <v>7.788939912271153</v>
+        <v>7.818930629857103</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478857455344056</v>
+        <v>0.747928966393503</v>
       </c>
       <c r="G7" t="n">
-        <v>30.31756074184557</v>
+        <v>30.39488081114119</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40274429458265</v>
+        <v>34.40473245410114</v>
       </c>
       <c r="I7" t="n">
-        <v>3.189792211422129</v>
+        <v>3.203369934551334</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674285909590034</v>
+        <v>4.674556039959394</v>
       </c>
       <c r="K7" t="n">
-        <v>16.88996586581528</v>
+        <v>16.76161056257239</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21281765817053</v>
+        <v>42.22848732335323</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89380944730578</v>
+        <v>99.89335780380537</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.11304085649898</v>
+        <v>87.87168558732601</v>
       </c>
       <c r="C8" t="n">
-        <v>43.10172769926003</v>
+        <v>43.10382708776536</v>
       </c>
       <c r="D8" t="n">
-        <v>1.993155514919025</v>
+        <v>1.99816336181632</v>
       </c>
       <c r="E8" t="n">
-        <v>9.634596180731766</v>
+        <v>9.576831055934711</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495140895715329</v>
+        <v>0.7494941334334302</v>
       </c>
       <c r="G8" t="n">
-        <v>30.81830571532426</v>
+        <v>30.8695405376851</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4776481202905</v>
+        <v>34.47673013793779</v>
       </c>
       <c r="I8" t="n">
-        <v>5.755358175839831</v>
+        <v>5.516588026559736</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68446305982208</v>
+        <v>4.684338333958939</v>
       </c>
       <c r="K8" t="n">
-        <v>11.886959143501</v>
+        <v>12.12831441267399</v>
       </c>
       <c r="L8" t="n">
-        <v>44.819884674882</v>
+        <v>44.58435624131871</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80857151764303</v>
+        <v>99.81649774175806</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.13148477600571</v>
+        <v>85.75867409223427</v>
       </c>
       <c r="C9" t="n">
-        <v>42.01337072225328</v>
+        <v>41.84721037524444</v>
       </c>
       <c r="D9" t="n">
-        <v>1.903640239185275</v>
+        <v>1.902087781008426</v>
       </c>
       <c r="E9" t="n">
-        <v>10.00273536773032</v>
+        <v>9.883922701842875</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7509078706945784</v>
+        <v>0.7508357701909401</v>
       </c>
       <c r="G9" t="n">
-        <v>29.43421445244739</v>
+        <v>29.38527298824159</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5417620519506</v>
+        <v>34.53844542878324</v>
       </c>
       <c r="I9" t="n">
-        <v>4.805050602156445</v>
+        <v>4.605385858473826</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693174191841115</v>
+        <v>4.692723563693376</v>
       </c>
       <c r="K9" t="n">
-        <v>13.86851522399427</v>
+        <v>14.24132590776575</v>
       </c>
       <c r="L9" t="n">
-        <v>43.95824299331244</v>
+        <v>43.7582251606965</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84012893956</v>
+        <v>99.84676144370668</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.06142506550628</v>
+        <v>83.35522588917794</v>
       </c>
       <c r="C10" t="n">
-        <v>40.68880635874652</v>
+        <v>40.15830796301553</v>
       </c>
       <c r="D10" t="n">
-        <v>1.811194527053807</v>
+        <v>1.793802958550556</v>
       </c>
       <c r="E10" t="n">
-        <v>10.18540604841981</v>
+        <v>9.961856460960126</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7521020663821486</v>
+        <v>0.7519898681652757</v>
       </c>
       <c r="G10" t="n">
-        <v>28.00481258329409</v>
+        <v>27.71238538537775</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59669505357883</v>
+        <v>34.59153393560268</v>
       </c>
       <c r="I10" t="n">
-        <v>4.010576871889155</v>
+        <v>3.843720604488575</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700637914888429</v>
+        <v>4.699936676032974</v>
       </c>
       <c r="K10" t="n">
-        <v>15.93857493449372</v>
+        <v>16.64477411082207</v>
       </c>
       <c r="L10" t="n">
-        <v>43.23914507892209</v>
+        <v>43.0689905412048</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86652637216233</v>
+        <v>99.8720726150424</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.77056418388348</v>
+        <v>80.83609659882393</v>
       </c>
       <c r="C11" t="n">
-        <v>39.01967890906722</v>
+        <v>38.23475546665645</v>
       </c>
       <c r="D11" t="n">
-        <v>1.709797767358805</v>
+        <v>1.681530789520257</v>
       </c>
       <c r="E11" t="n">
-        <v>10.17297726568926</v>
+        <v>9.872910876545067</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7531281345672967</v>
+        <v>0.7529844258340966</v>
       </c>
       <c r="G11" t="n">
-        <v>26.43700900979784</v>
+        <v>25.97789743541141</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64389419009564</v>
+        <v>34.63728358836845</v>
       </c>
       <c r="I11" t="n">
-        <v>3.346706975329038</v>
+        <v>3.207336821681533</v>
       </c>
       <c r="J11" t="n">
-        <v>4.707050841045604</v>
+        <v>4.706152661463105</v>
       </c>
       <c r="K11" t="n">
-        <v>18.22943581611651</v>
+        <v>19.16390340117607</v>
       </c>
       <c r="L11" t="n">
-        <v>42.63948036170822</v>
+        <v>42.49457111537614</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88859508689197</v>
+        <v>99.89322998320867</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.33046264579394</v>
+        <v>78.2884462229343</v>
       </c>
       <c r="C12" t="n">
-        <v>37.0976310525638</v>
+        <v>36.18313659887698</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6028006662115</v>
+        <v>1.569176218078388</v>
       </c>
       <c r="E12" t="n">
-        <v>10.00173026075844</v>
+        <v>9.659205148446503</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7540117296758763</v>
+        <v>0.7538423025889707</v>
       </c>
       <c r="G12" t="n">
-        <v>24.78261257704125</v>
+        <v>24.2421364541039</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6845395650903</v>
+        <v>34.67674591909265</v>
       </c>
       <c r="I12" t="n">
-        <v>2.792194536542354</v>
+        <v>2.675825789442813</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712573310474228</v>
+        <v>4.711514391181067</v>
       </c>
       <c r="K12" t="n">
-        <v>20.66953735420606</v>
+        <v>21.7115537770657</v>
       </c>
       <c r="L12" t="n">
-        <v>42.13986751058211</v>
+        <v>42.01621693456617</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90703591735196</v>
+        <v>99.91090731050885</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.00136458392913</v>
+        <v>75.78317968465558</v>
       </c>
       <c r="C13" t="n">
-        <v>35.19986196856426</v>
+        <v>34.090736055695</v>
       </c>
       <c r="D13" t="n">
-        <v>1.501719922808338</v>
+        <v>1.459777772417596</v>
       </c>
       <c r="E13" t="n">
-        <v>9.759166210565327</v>
+        <v>9.357800527663487</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547719868441127</v>
+        <v>0.754582400507481</v>
       </c>
       <c r="G13" t="n">
-        <v>23.21969526887656</v>
+        <v>22.55204453388382</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71951139482917</v>
+        <v>34.71079042334413</v>
       </c>
       <c r="I13" t="n">
-        <v>2.329174882229924</v>
+        <v>2.232044023667314</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717324917775705</v>
+        <v>4.716140003171757</v>
       </c>
       <c r="K13" t="n">
-        <v>22.99863541607086</v>
+        <v>24.21682031534441</v>
       </c>
       <c r="L13" t="n">
-        <v>41.72394165601649</v>
+        <v>41.6181151348094</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92243904065161</v>
+        <v>99.92567150584881</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.61932357014702</v>
+        <v>82.99645373918764</v>
       </c>
       <c r="C14" t="n">
-        <v>39.187281358839</v>
+        <v>38.45796602470541</v>
       </c>
       <c r="D14" t="n">
-        <v>1.503624883005786</v>
+        <v>1.461597309818851</v>
       </c>
       <c r="E14" t="n">
-        <v>12.01519817442148</v>
+        <v>11.79767279516038</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7557294294212861</v>
+        <v>0.7555229483949711</v>
       </c>
       <c r="G14" t="n">
-        <v>24.96243868145689</v>
+        <v>24.49110883450186</v>
       </c>
       <c r="H14" t="n">
-        <v>36.47684254222288</v>
+        <v>36.66500997109377</v>
       </c>
       <c r="I14" t="n">
-        <v>3.182180925735663</v>
+        <v>3.103523452749238</v>
       </c>
       <c r="J14" t="n">
-        <v>4.723308933883039</v>
+        <v>4.72201842746857</v>
       </c>
       <c r="K14" t="n">
-        <v>16.38067642985297</v>
+        <v>17.00354626081235</v>
       </c>
       <c r="L14" t="n">
-        <v>44.32610389854203</v>
+        <v>44.43516571824188</v>
       </c>
       <c r="M14" t="n">
-        <v>99.894061687234</v>
+        <v>99.89667800375966</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.90168563329669</v>
+        <v>82.09858655879168</v>
       </c>
       <c r="C15" t="n">
-        <v>38.96132280447395</v>
+        <v>38.03907963147304</v>
       </c>
       <c r="D15" t="n">
-        <v>1.477158768315685</v>
+        <v>1.428334054204083</v>
       </c>
       <c r="E15" t="n">
-        <v>12.24615349986377</v>
+        <v>11.96067757497002</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7565360859526402</v>
+        <v>0.7563171317646022</v>
       </c>
       <c r="G15" t="n">
-        <v>24.52306129913573</v>
+        <v>23.93373642557747</v>
       </c>
       <c r="H15" t="n">
-        <v>36.51577748657511</v>
+        <v>36.70355114476462</v>
       </c>
       <c r="I15" t="n">
-        <v>2.654647956249749</v>
+        <v>2.58898815398213</v>
       </c>
       <c r="J15" t="n">
-        <v>4.728350537204002</v>
+        <v>4.726982073528765</v>
       </c>
       <c r="K15" t="n">
-        <v>17.0983143667033</v>
+        <v>17.90141344120832</v>
       </c>
       <c r="L15" t="n">
-        <v>43.85196891421897</v>
+        <v>43.97329794252004</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91160608539622</v>
+        <v>99.91379101520141</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.52674957943029</v>
+        <v>79.43368150299892</v>
       </c>
       <c r="C16" t="n">
-        <v>36.9966747044361</v>
+        <v>35.77374181877649</v>
       </c>
       <c r="D16" t="n">
-        <v>1.386703369569243</v>
+        <v>1.327550589762776</v>
       </c>
       <c r="E16" t="n">
-        <v>11.86528622123783</v>
+        <v>11.47663791193366</v>
       </c>
       <c r="F16" t="n">
-        <v>0.757229498649353</v>
+        <v>0.7570024940177643</v>
       </c>
       <c r="G16" t="n">
-        <v>23.02136538406081</v>
+        <v>22.2449684046127</v>
       </c>
       <c r="H16" t="n">
-        <v>36.54924648324253</v>
+        <v>36.73681130436584</v>
       </c>
       <c r="I16" t="n">
-        <v>2.214234256112058</v>
+        <v>2.159445210695155</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732684366558456</v>
+        <v>4.731265587611028</v>
       </c>
       <c r="K16" t="n">
-        <v>19.47325042056972</v>
+        <v>20.56631849700107</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45633465398723</v>
+        <v>43.58802334661183</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92625977899306</v>
+        <v>99.92808366238938</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.19342338702191</v>
+        <v>81.04710531511223</v>
       </c>
       <c r="C17" t="n">
-        <v>38.19710888935002</v>
+        <v>36.93119602219875</v>
       </c>
       <c r="D17" t="n">
-        <v>1.387966083939136</v>
+        <v>1.328750178681899</v>
       </c>
       <c r="E17" t="n">
-        <v>12.64699462109288</v>
+        <v>12.23312251239843</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7579190221554135</v>
+        <v>0.7576865295720967</v>
       </c>
       <c r="G17" t="n">
-        <v>23.43901096145823</v>
+        <v>22.64500822547535</v>
       </c>
       <c r="H17" t="n">
-        <v>36.97921037631797</v>
+        <v>37.14994610955096</v>
       </c>
       <c r="I17" t="n">
-        <v>2.245328433586952</v>
+        <v>2.197050949607882</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736993888471335</v>
+        <v>4.735540809825605</v>
       </c>
       <c r="K17" t="n">
-        <v>17.80657661297808</v>
+        <v>18.95289468488778</v>
       </c>
       <c r="L17" t="n">
-        <v>43.92153830679631</v>
+        <v>44.04274037747484</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9252238091244</v>
+        <v>99.92683108456137</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.93137850166686</v>
+        <v>78.53239784059218</v>
       </c>
       <c r="C18" t="n">
-        <v>36.28169697462211</v>
+        <v>34.75500593683107</v>
       </c>
       <c r="D18" t="n">
-        <v>1.305202602326505</v>
+        <v>1.237424985021738</v>
       </c>
       <c r="E18" t="n">
-        <v>12.20495755828113</v>
+        <v>11.69772150222859</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7585108861085561</v>
+        <v>0.7582758017904555</v>
       </c>
       <c r="G18" t="n">
-        <v>22.04135854388521</v>
+        <v>21.08861350598115</v>
       </c>
       <c r="H18" t="n">
-        <v>37.00808768510378</v>
+        <v>37.17883857404844</v>
       </c>
       <c r="I18" t="n">
-        <v>1.872568187783202</v>
+        <v>1.832299710331456</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740693038178476</v>
+        <v>4.739223761190347</v>
       </c>
       <c r="K18" t="n">
-        <v>20.06862149833315</v>
+        <v>21.46760215940781</v>
       </c>
       <c r="L18" t="n">
-        <v>43.58731129277843</v>
+        <v>43.71636271071647</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9376297657337</v>
+        <v>99.93897080695535</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.02746375541273</v>
+        <v>77.49471996963443</v>
       </c>
       <c r="C19" t="n">
-        <v>35.66619375931716</v>
+        <v>33.99884399494356</v>
       </c>
       <c r="D19" t="n">
-        <v>1.27285497961257</v>
+        <v>1.200473676084376</v>
       </c>
       <c r="E19" t="n">
-        <v>12.16272495077193</v>
+        <v>11.60306385566809</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7590104658977606</v>
+        <v>0.7587741517493668</v>
       </c>
       <c r="G19" t="n">
-        <v>21.49509427118971</v>
+        <v>20.4588768494949</v>
       </c>
       <c r="H19" t="n">
-        <v>37.03246240797617</v>
+        <v>37.20327305109755</v>
       </c>
       <c r="I19" t="n">
-        <v>1.561501268103577</v>
+        <v>1.527919937106606</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743815411861004</v>
+        <v>4.742338448433543</v>
       </c>
       <c r="K19" t="n">
-        <v>20.97253624458727</v>
+        <v>22.50528003036557</v>
       </c>
       <c r="L19" t="n">
-        <v>43.3092542131016</v>
+        <v>43.444978760515</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94798421700602</v>
+        <v>99.94910278582412</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.58923442705354</v>
+        <v>74.85673443589211</v>
       </c>
       <c r="C20" t="n">
-        <v>33.46833051523826</v>
+        <v>31.59541410163035</v>
       </c>
       <c r="D20" t="n">
-        <v>1.184678137046353</v>
+        <v>1.105893168367966</v>
       </c>
       <c r="E20" t="n">
-        <v>11.53715202788561</v>
+        <v>10.90123646616096</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7594405623909756</v>
+        <v>0.7592046050609703</v>
       </c>
       <c r="G20" t="n">
-        <v>20.0060247590654</v>
+        <v>18.84700397107893</v>
       </c>
       <c r="H20" t="n">
-        <v>37.05344700954942</v>
+        <v>37.22437850395255</v>
       </c>
       <c r="I20" t="n">
-        <v>1.301988416172182</v>
+        <v>1.273988939639675</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746503514943598</v>
+        <v>4.745028781631065</v>
       </c>
       <c r="K20" t="n">
-        <v>23.41076557294648</v>
+        <v>25.14326556410787</v>
       </c>
       <c r="L20" t="n">
-        <v>43.07752887659015</v>
+        <v>43.2188781137866</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95662496477487</v>
+        <v>99.95755777952482</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.16994979941339</v>
+        <v>80.98289901525446</v>
       </c>
       <c r="C21" t="n">
-        <v>36.85334518722318</v>
+        <v>35.34967614303822</v>
       </c>
       <c r="D21" t="n">
-        <v>1.185606449542671</v>
+        <v>1.106754229296583</v>
       </c>
       <c r="E21" t="n">
-        <v>13.39150690213328</v>
+        <v>12.93698333857631</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7600356591875082</v>
+        <v>0.7597957303531258</v>
       </c>
       <c r="G21" t="n">
-        <v>21.54507441746048</v>
+        <v>20.57366650246437</v>
       </c>
       <c r="H21" t="n">
-        <v>38.60585500943005</v>
+        <v>38.96534986699862</v>
       </c>
       <c r="I21" t="n">
-        <v>1.931648491737457</v>
+        <v>1.891626032858417</v>
       </c>
       <c r="J21" t="n">
-        <v>4.750222869921926</v>
+        <v>4.748723314707036</v>
       </c>
       <c r="K21" t="n">
-        <v>17.83005020058662</v>
+        <v>19.01710098474552</v>
       </c>
       <c r="L21" t="n">
-        <v>45.25226674421549</v>
+        <v>45.57021772763912</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9356621320253</v>
+        <v>99.93699485542285</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_43_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.59528117768797</v>
+        <v>45.26963565373095</v>
       </c>
       <c r="M2" t="n">
-        <v>99.18835417531764</v>
+        <v>99.67475990963985</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.07729418420487</v>
+        <v>88.08336138501713</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93550090214011</v>
+        <v>45.93586169442141</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228853606003148</v>
+        <v>2.228868879778536</v>
       </c>
       <c r="E3" t="n">
-        <v>5.713035333018638</v>
+        <v>5.713582780601864</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429512020010495</v>
+        <v>0.7429562932595121</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97495437118376</v>
+        <v>33.97501396157126</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17575529204827</v>
+        <v>34.17598948993755</v>
       </c>
       <c r="I3" t="n">
-        <v>6.598299367443448</v>
+        <v>6.603473146996446</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643445012506559</v>
+        <v>4.64347683287195</v>
       </c>
       <c r="K3" t="n">
-        <v>11.92270581579513</v>
+        <v>11.91663861498288</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90496124070784</v>
+        <v>48.91048357154423</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7631679586431</v>
+        <v>106.7629838809485</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.13549538800527</v>
+        <v>87.24616117268536</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63442618370748</v>
+        <v>42.74037075107339</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183367758091176</v>
+        <v>2.188954748834281</v>
       </c>
       <c r="E4" t="n">
-        <v>6.514807443394666</v>
+        <v>6.530346462803633</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744517264837297</v>
+        <v>0.7445216051824087</v>
       </c>
       <c r="G4" t="n">
-        <v>33.28160259465543</v>
+        <v>33.36659631601206</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24779418251565</v>
+        <v>34.2479938383908</v>
       </c>
       <c r="I4" t="n">
-        <v>5.510173239277926</v>
+        <v>5.514488169072141</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653232905233106</v>
+        <v>4.653260032390054</v>
       </c>
       <c r="K4" t="n">
-        <v>12.86450461199473</v>
+        <v>12.75383882731462</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31778311075771</v>
+        <v>44.3223606119732</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81671390645991</v>
+        <v>99.81657019036122</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.02431116746617</v>
+        <v>86.22132410626858</v>
       </c>
       <c r="C5" t="n">
-        <v>42.37841267922806</v>
+        <v>42.57148320100895</v>
       </c>
       <c r="D5" t="n">
-        <v>2.129363790049084</v>
+        <v>2.139452272747032</v>
       </c>
       <c r="E5" t="n">
-        <v>7.120334498775237</v>
+        <v>7.149929123072075</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458443223250675</v>
+        <v>0.7458466713832966</v>
       </c>
       <c r="G5" t="n">
-        <v>32.45840705361532</v>
+        <v>32.61202195255118</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3088388269531</v>
+        <v>34.30894688363164</v>
       </c>
       <c r="I5" t="n">
-        <v>4.599995661216676</v>
+        <v>4.603585506737741</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661527014531672</v>
+        <v>4.661541696145603</v>
       </c>
       <c r="K5" t="n">
-        <v>13.97568883253383</v>
+        <v>13.77867589373141</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49283812048036</v>
+        <v>43.49666067834097</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84693963224227</v>
+        <v>99.84681977308134</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.73387096884017</v>
+        <v>85.03445750097403</v>
       </c>
       <c r="C6" t="n">
-        <v>41.8023977524188</v>
+        <v>42.09977029039482</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066598117542234</v>
+        <v>2.081982757740614</v>
       </c>
       <c r="E6" t="n">
-        <v>7.550306872400611</v>
+        <v>7.598219090648049</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469707452155965</v>
+        <v>0.7469699873204982</v>
       </c>
       <c r="G6" t="n">
-        <v>31.50165473316082</v>
+        <v>31.73600470792001</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36065427991743</v>
+        <v>34.36061941674291</v>
       </c>
       <c r="I6" t="n">
-        <v>3.839119063005979</v>
+        <v>3.842099119848816</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668567157597479</v>
+        <v>4.668562420753113</v>
       </c>
       <c r="K6" t="n">
-        <v>15.26612903115984</v>
+        <v>14.96554249902598</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80369555916533</v>
+        <v>42.80680983539203</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87222234274398</v>
+        <v>99.87212262481283</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.23838943742761</v>
+        <v>83.62321701746632</v>
       </c>
       <c r="C7" t="n">
-        <v>40.90325991787976</v>
+        <v>41.28556093787823</v>
       </c>
       <c r="D7" t="n">
-        <v>1.993990601423949</v>
+        <v>2.01360992754856</v>
       </c>
       <c r="E7" t="n">
-        <v>7.818930629857103</v>
+        <v>7.882998483200354</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747928966393503</v>
+        <v>0.7479245335626269</v>
       </c>
       <c r="G7" t="n">
-        <v>30.39488081114119</v>
+        <v>30.69378644131744</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40473245410114</v>
+        <v>34.40452854388084</v>
       </c>
       <c r="I7" t="n">
-        <v>3.203369934551334</v>
+        <v>3.205840753190067</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674556039959394</v>
+        <v>4.674528334766417</v>
       </c>
       <c r="K7" t="n">
-        <v>16.76161056257239</v>
+        <v>16.3767829825337</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22848732335323</v>
+        <v>42.23093110403671</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89335780380537</v>
+        <v>99.89327502444864</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.87168558732601</v>
+        <v>88.51909183299757</v>
       </c>
       <c r="C8" t="n">
-        <v>43.10382708776536</v>
+        <v>43.57093313680109</v>
       </c>
       <c r="D8" t="n">
-        <v>1.99816336181632</v>
+        <v>2.01792589552712</v>
       </c>
       <c r="E8" t="n">
-        <v>9.576831055934711</v>
+        <v>9.707713752345192</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494941334334302</v>
+        <v>0.7495276336929317</v>
       </c>
       <c r="G8" t="n">
-        <v>30.8695405376851</v>
+        <v>31.18915571671879</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47673013793779</v>
+        <v>34.47827114987486</v>
       </c>
       <c r="I8" t="n">
-        <v>5.516588026559736</v>
+        <v>5.691949974257865</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684338333958939</v>
+        <v>4.684547710580822</v>
       </c>
       <c r="K8" t="n">
-        <v>12.12831441267399</v>
+        <v>11.48090816700241</v>
       </c>
       <c r="L8" t="n">
-        <v>44.58435624131871</v>
+        <v>44.75883283111427</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81649774175806</v>
+        <v>99.81067413491778</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.75867409223427</v>
+        <v>86.77100853281861</v>
       </c>
       <c r="C9" t="n">
-        <v>41.84721037524444</v>
+        <v>42.70678830564086</v>
       </c>
       <c r="D9" t="n">
-        <v>1.902087781008426</v>
+        <v>1.939261701165674</v>
       </c>
       <c r="E9" t="n">
-        <v>9.883922701842875</v>
+        <v>10.1212726202722</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508357701909401</v>
+        <v>0.7508958779966272</v>
       </c>
       <c r="G9" t="n">
-        <v>29.38527298824159</v>
+        <v>29.97331830033612</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53844542878324</v>
+        <v>34.54121038784485</v>
       </c>
       <c r="I9" t="n">
-        <v>4.605385858473826</v>
+        <v>4.751950407724222</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692723563693376</v>
+        <v>4.693099237478918</v>
       </c>
       <c r="K9" t="n">
-        <v>14.24132590776575</v>
+        <v>13.22899146718139</v>
       </c>
       <c r="L9" t="n">
-        <v>43.7582251606965</v>
+        <v>43.90611050567057</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84676144370668</v>
+        <v>99.84189027849281</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.35522588917794</v>
+        <v>84.93370522915275</v>
       </c>
       <c r="C10" t="n">
-        <v>40.15830796301553</v>
+        <v>41.60743830828869</v>
       </c>
       <c r="D10" t="n">
-        <v>1.793802958550556</v>
+        <v>1.857383033746107</v>
       </c>
       <c r="E10" t="n">
-        <v>9.961856460960126</v>
+        <v>10.35495706099387</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519898681652757</v>
+        <v>0.7520646896332689</v>
       </c>
       <c r="G10" t="n">
-        <v>27.71238538537775</v>
+        <v>28.70779784010178</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59153393560268</v>
+        <v>34.59497572313037</v>
       </c>
       <c r="I10" t="n">
-        <v>3.843720604488575</v>
+        <v>3.96612257133944</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699936676032974</v>
+        <v>4.700404310207929</v>
       </c>
       <c r="K10" t="n">
-        <v>16.64477411082207</v>
+        <v>15.06629477084724</v>
       </c>
       <c r="L10" t="n">
-        <v>43.0689905412048</v>
+        <v>43.19426829842729</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8720726150424</v>
+        <v>99.86800137756322</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.83609659882393</v>
+        <v>82.95954112187134</v>
       </c>
       <c r="C11" t="n">
-        <v>38.23475546665645</v>
+        <v>40.24888887432407</v>
       </c>
       <c r="D11" t="n">
-        <v>1.681530789520257</v>
+        <v>1.770125580347782</v>
       </c>
       <c r="E11" t="n">
-        <v>9.872910876545067</v>
+        <v>10.42007742468345</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529844258340966</v>
+        <v>0.7530647578235693</v>
       </c>
       <c r="G11" t="n">
-        <v>25.97789743541141</v>
+        <v>27.35914261568691</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63728358836845</v>
+        <v>34.64097885988419</v>
       </c>
       <c r="I11" t="n">
-        <v>3.207336821681533</v>
+        <v>3.309497147048128</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706152661463105</v>
+        <v>4.706654736397307</v>
       </c>
       <c r="K11" t="n">
-        <v>19.16390340117607</v>
+        <v>17.04045887812867</v>
       </c>
       <c r="L11" t="n">
-        <v>42.49457111537614</v>
+        <v>42.60048217612116</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89322998320867</v>
+        <v>99.8898299285739</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.2884462229343</v>
+        <v>80.88932056151349</v>
       </c>
       <c r="C12" t="n">
-        <v>36.18313659887698</v>
+        <v>38.69184219971832</v>
       </c>
       <c r="D12" t="n">
-        <v>1.569176218078388</v>
+        <v>1.679376512909795</v>
       </c>
       <c r="E12" t="n">
-        <v>9.659205148446503</v>
+        <v>10.34604645344335</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538423025889707</v>
+        <v>0.7539215875033851</v>
       </c>
       <c r="G12" t="n">
-        <v>24.2421364541039</v>
+        <v>25.95652084362673</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67674591909265</v>
+        <v>34.68039302515572</v>
       </c>
       <c r="I12" t="n">
-        <v>2.675825789442813</v>
+        <v>2.761052216978364</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711514391181067</v>
+        <v>4.712009921896156</v>
       </c>
       <c r="K12" t="n">
-        <v>21.7115537770657</v>
+        <v>19.11067943848652</v>
       </c>
       <c r="L12" t="n">
-        <v>42.01621693456617</v>
+        <v>42.10554788548826</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91090731050885</v>
+        <v>99.9080695236931</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.78317968465558</v>
+        <v>78.76391780569558</v>
       </c>
       <c r="C13" t="n">
-        <v>34.090736055695</v>
+        <v>36.99394211624568</v>
       </c>
       <c r="D13" t="n">
-        <v>1.459777772417596</v>
+        <v>1.586946837705513</v>
       </c>
       <c r="E13" t="n">
-        <v>9.357800527663487</v>
+        <v>10.16047306980196</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754582400507481</v>
+        <v>0.7546564296981658</v>
       </c>
       <c r="G13" t="n">
-        <v>22.55204453388382</v>
+        <v>24.5279235204138</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71079042334413</v>
+        <v>34.71419576611563</v>
       </c>
       <c r="I13" t="n">
-        <v>2.232044023667314</v>
+        <v>2.303119496346983</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716140003171757</v>
+        <v>4.716602685613535</v>
       </c>
       <c r="K13" t="n">
-        <v>24.21682031534441</v>
+        <v>21.23608219430443</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6181151348094</v>
+        <v>41.69327979453384</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92567150584881</v>
+        <v>99.92330410508394</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.99645373918764</v>
+        <v>84.81828295395843</v>
       </c>
       <c r="C14" t="n">
-        <v>38.45796602470541</v>
+        <v>40.70333338819507</v>
       </c>
       <c r="D14" t="n">
-        <v>1.461597309818851</v>
+        <v>1.588818386982502</v>
       </c>
       <c r="E14" t="n">
-        <v>11.79767279516038</v>
+        <v>12.26136244089273</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555229483949711</v>
+        <v>0.7555464259235082</v>
       </c>
       <c r="G14" t="n">
-        <v>24.49110883450186</v>
+        <v>26.14560918803602</v>
       </c>
       <c r="H14" t="n">
-        <v>36.66500997109377</v>
+        <v>36.34389450815453</v>
       </c>
       <c r="I14" t="n">
-        <v>3.103523452749238</v>
+        <v>3.00088684194722</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72201842746857</v>
+        <v>4.722165162021924</v>
       </c>
       <c r="K14" t="n">
-        <v>17.00354626081235</v>
+        <v>15.18171704604155</v>
       </c>
       <c r="L14" t="n">
-        <v>44.43516571824188</v>
+        <v>44.01503783422844</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89667800375966</v>
+        <v>99.90008826846507</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.09858655879168</v>
+        <v>84.27394312186176</v>
       </c>
       <c r="C15" t="n">
-        <v>38.03907963147304</v>
+        <v>40.62378644889742</v>
       </c>
       <c r="D15" t="n">
-        <v>1.428334054204083</v>
+        <v>1.568746378386631</v>
       </c>
       <c r="E15" t="n">
-        <v>11.96067757497002</v>
+        <v>12.52366356067659</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563171317646022</v>
+        <v>0.7562945002426544</v>
       </c>
       <c r="G15" t="n">
-        <v>23.93373642557747</v>
+        <v>25.81530404009318</v>
       </c>
       <c r="H15" t="n">
-        <v>36.70355114476462</v>
+        <v>36.37987897344543</v>
       </c>
       <c r="I15" t="n">
-        <v>2.58898815398213</v>
+        <v>2.503215042500689</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726982073528765</v>
+        <v>4.726840626516588</v>
       </c>
       <c r="K15" t="n">
-        <v>17.90141344120832</v>
+        <v>15.72605687813823</v>
       </c>
       <c r="L15" t="n">
-        <v>43.97329794252004</v>
+        <v>43.56679870513247</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91379101520141</v>
+        <v>99.91664203216813</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.43368150299892</v>
+        <v>82.11777972640969</v>
       </c>
       <c r="C16" t="n">
-        <v>35.77374181877649</v>
+        <v>38.85551383984987</v>
       </c>
       <c r="D16" t="n">
-        <v>1.327550589762776</v>
+        <v>1.485246634408208</v>
       </c>
       <c r="E16" t="n">
-        <v>11.47663791193366</v>
+        <v>12.20502927383109</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570024940177643</v>
+        <v>0.7569354401308147</v>
       </c>
       <c r="G16" t="n">
-        <v>22.2449684046127</v>
+        <v>24.44123152730764</v>
       </c>
       <c r="H16" t="n">
-        <v>36.73681130436584</v>
+        <v>36.41070997321211</v>
       </c>
       <c r="I16" t="n">
-        <v>2.159445210695155</v>
+        <v>2.087780376702246</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731265587611028</v>
+        <v>4.73084650081759</v>
       </c>
       <c r="K16" t="n">
-        <v>20.56631849700107</v>
+        <v>17.88222027359029</v>
       </c>
       <c r="L16" t="n">
-        <v>43.58802334661183</v>
+        <v>43.19273213537926</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92808366238938</v>
+        <v>99.93046624881941</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.04710531511223</v>
+        <v>83.65495119433415</v>
       </c>
       <c r="C17" t="n">
-        <v>36.93119602219875</v>
+        <v>39.98308551576611</v>
       </c>
       <c r="D17" t="n">
-        <v>1.328750178681899</v>
+        <v>1.48648299027664</v>
       </c>
       <c r="E17" t="n">
-        <v>12.23312251239843</v>
+        <v>12.93705706734491</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576865295720967</v>
+        <v>0.7575655318285498</v>
       </c>
       <c r="G17" t="n">
-        <v>22.64500822547535</v>
+        <v>24.83526283116846</v>
       </c>
       <c r="H17" t="n">
-        <v>37.14994610955096</v>
+        <v>36.81470496564547</v>
       </c>
       <c r="I17" t="n">
-        <v>2.197050949607882</v>
+        <v>2.08909323414169</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735540809825605</v>
+        <v>4.734784573928434</v>
       </c>
       <c r="K17" t="n">
-        <v>18.95289468488778</v>
+        <v>16.34504880566585</v>
       </c>
       <c r="L17" t="n">
-        <v>44.04274037747484</v>
+        <v>43.60228715630507</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92683108456137</v>
+        <v>99.93042147773704</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.53239784059218</v>
+        <v>81.55709379503729</v>
       </c>
       <c r="C18" t="n">
-        <v>34.75500593683107</v>
+        <v>38.20866285939696</v>
       </c>
       <c r="D18" t="n">
-        <v>1.237424985021738</v>
+        <v>1.408052248428406</v>
       </c>
       <c r="E18" t="n">
-        <v>11.69772150222859</v>
+        <v>12.54482243750125</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582758017904555</v>
+        <v>0.7581049466936499</v>
       </c>
       <c r="G18" t="n">
-        <v>21.08861350598115</v>
+        <v>23.52488921735273</v>
       </c>
       <c r="H18" t="n">
-        <v>37.17883857404844</v>
+        <v>36.84091840630295</v>
       </c>
       <c r="I18" t="n">
-        <v>1.832299710331456</v>
+        <v>1.742150621923007</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739223761190347</v>
+        <v>4.73815591683531</v>
       </c>
       <c r="K18" t="n">
-        <v>21.46760215940781</v>
+        <v>18.44290620496269</v>
       </c>
       <c r="L18" t="n">
-        <v>43.71636271071647</v>
+        <v>43.29040056802531</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93897080695535</v>
+        <v>99.94196963238497</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.49471996963443</v>
+        <v>80.70536875674097</v>
       </c>
       <c r="C19" t="n">
-        <v>33.99884399494356</v>
+        <v>37.62610917583564</v>
       </c>
       <c r="D19" t="n">
-        <v>1.200473676084376</v>
+        <v>1.376878263668279</v>
       </c>
       <c r="E19" t="n">
-        <v>11.60306385566809</v>
+        <v>12.50919321047923</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587741517493668</v>
+        <v>0.7585597992043964</v>
       </c>
       <c r="G19" t="n">
-        <v>20.4588768494949</v>
+        <v>23.00405304897618</v>
       </c>
       <c r="H19" t="n">
-        <v>37.20327305109755</v>
+        <v>36.86302244916456</v>
       </c>
       <c r="I19" t="n">
-        <v>1.527919937106606</v>
+        <v>1.452663240220837</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742338448433543</v>
+        <v>4.740998745027476</v>
       </c>
       <c r="K19" t="n">
-        <v>22.50528003036557</v>
+        <v>19.29463124325905</v>
       </c>
       <c r="L19" t="n">
-        <v>43.444978760515</v>
+        <v>43.03086650807411</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94910278582412</v>
+        <v>99.9516069271688</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.85673443589211</v>
+        <v>78.42214757340527</v>
       </c>
       <c r="C20" t="n">
-        <v>31.59541410163035</v>
+        <v>35.56722192235641</v>
       </c>
       <c r="D20" t="n">
-        <v>1.105893168367966</v>
+        <v>1.292324817224068</v>
       </c>
       <c r="E20" t="n">
-        <v>10.90123646616096</v>
+        <v>11.94287219101505</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592046050609703</v>
+        <v>0.7589503136104561</v>
       </c>
       <c r="G20" t="n">
-        <v>18.84700397107893</v>
+        <v>21.5913849730823</v>
       </c>
       <c r="H20" t="n">
-        <v>37.22437850395255</v>
+        <v>36.88199991321208</v>
       </c>
       <c r="I20" t="n">
-        <v>1.273988939639675</v>
+        <v>1.211175905195965</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745028781631065</v>
+        <v>4.743439460065348</v>
       </c>
       <c r="K20" t="n">
-        <v>25.14326556410787</v>
+        <v>21.57785242659473</v>
       </c>
       <c r="L20" t="n">
-        <v>43.2188781137866</v>
+        <v>42.81457389437607</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95755777952482</v>
+        <v>99.95964824332721</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.98289901525446</v>
+        <v>83.58000457459198</v>
       </c>
       <c r="C21" t="n">
-        <v>35.34967614303822</v>
+        <v>38.69842705138706</v>
       </c>
       <c r="D21" t="n">
-        <v>1.106754229296583</v>
+        <v>1.29324761034948</v>
       </c>
       <c r="E21" t="n">
-        <v>12.93698333857631</v>
+        <v>13.65816099259734</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597957303531258</v>
+        <v>0.7594922471263916</v>
       </c>
       <c r="G21" t="n">
-        <v>20.57366650246437</v>
+        <v>23.01515907036606</v>
       </c>
       <c r="H21" t="n">
-        <v>38.96534986699862</v>
+        <v>38.31669237572572</v>
       </c>
       <c r="I21" t="n">
-        <v>1.891626032858417</v>
+        <v>1.790425733887043</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748723314707036</v>
+        <v>4.746826544539945</v>
       </c>
       <c r="K21" t="n">
-        <v>19.01710098474552</v>
+        <v>16.41999542540805</v>
       </c>
       <c r="L21" t="n">
-        <v>45.57021772763912</v>
+        <v>44.82193925051366</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93699485542285</v>
+        <v>99.94036172730875</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_43_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.26963565373095</v>
+        <v>43.35614091906604</v>
       </c>
       <c r="M2" t="n">
-        <v>99.67475990963985</v>
+        <v>95.367260626199</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08336138501713</v>
+        <v>81.56240073634278</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93586169442141</v>
+        <v>43.31795629189835</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228868879778536</v>
+        <v>2.184612885922722</v>
       </c>
       <c r="E3" t="n">
-        <v>5.713582780601864</v>
+        <v>4.161680757089464</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429562932595121</v>
+        <v>0.7376932644570622</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97501396157126</v>
+        <v>32.86021882575429</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17598948993755</v>
+        <v>33.93389016502486</v>
       </c>
       <c r="I3" t="n">
-        <v>6.603473146996446</v>
+        <v>3.073721935237759</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64347683287195</v>
+        <v>4.610582902856638</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91663861498288</v>
+        <v>18.43759926365721</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91048357154423</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7629838809485</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.24616117268536</v>
+        <v>88.74097131706296</v>
       </c>
       <c r="C4" t="n">
-        <v>42.74037075107339</v>
+        <v>42.92131015679843</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188954748834281</v>
+        <v>2.190405610734226</v>
       </c>
       <c r="E4" t="n">
-        <v>6.530346462803633</v>
+        <v>6.554891184012786</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445216051824087</v>
+        <v>0.7396493337011079</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36659631601206</v>
+        <v>33.55017427816146</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2479938383908</v>
+        <v>34.02386935025095</v>
       </c>
       <c r="I4" t="n">
-        <v>5.514488169072141</v>
+        <v>7.059173224570491</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653260032390054</v>
+        <v>4.622808335631924</v>
       </c>
       <c r="K4" t="n">
-        <v>12.75383882731462</v>
+        <v>11.25902868293706</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3223606119732</v>
+        <v>45.58497767341345</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81657019036122</v>
+        <v>99.76531651314893</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.22132410626858</v>
+        <v>87.7609457494364</v>
       </c>
       <c r="C5" t="n">
-        <v>42.57148320100895</v>
+        <v>43.03553556461783</v>
       </c>
       <c r="D5" t="n">
-        <v>2.139452272747032</v>
+        <v>2.14444329101489</v>
       </c>
       <c r="E5" t="n">
-        <v>7.149929123072075</v>
+        <v>7.399983066797571</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458466713832966</v>
+        <v>0.7413056655887839</v>
       </c>
       <c r="G5" t="n">
-        <v>32.61202195255118</v>
+        <v>32.84617506027442</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30894688363164</v>
+        <v>34.10006061708405</v>
       </c>
       <c r="I5" t="n">
-        <v>4.603585506737741</v>
+        <v>5.895817638746776</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661541696145603</v>
+        <v>4.633160409929899</v>
       </c>
       <c r="K5" t="n">
-        <v>13.77867589373141</v>
+        <v>12.2390542505636</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49666067834097</v>
+        <v>44.52932203969162</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84681977308134</v>
+        <v>99.80391185487305</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.03445750097403</v>
+        <v>86.60273372691876</v>
       </c>
       <c r="C6" t="n">
-        <v>42.09977029039482</v>
+        <v>42.79255862209506</v>
       </c>
       <c r="D6" t="n">
-        <v>2.081982757740614</v>
+        <v>2.089803988355618</v>
       </c>
       <c r="E6" t="n">
-        <v>7.598219090648049</v>
+        <v>8.031850368411034</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469699873204982</v>
+        <v>0.7427101900993537</v>
       </c>
       <c r="G6" t="n">
-        <v>31.73600470792001</v>
+        <v>32.00927155816856</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36061941674291</v>
+        <v>34.16466874457026</v>
       </c>
       <c r="I6" t="n">
-        <v>3.842099119848816</v>
+        <v>4.922490189192966</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668562420753113</v>
+        <v>4.641938688120961</v>
       </c>
       <c r="K6" t="n">
-        <v>14.96554249902598</v>
+        <v>13.39726627308125</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80680983539203</v>
+        <v>43.64640239263627</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87212262481283</v>
+        <v>99.83622728781258</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.62321701746632</v>
+        <v>85.33599490587535</v>
       </c>
       <c r="C7" t="n">
-        <v>41.28556093787823</v>
+        <v>42.29057647693462</v>
       </c>
       <c r="D7" t="n">
-        <v>2.01360992754856</v>
+        <v>2.030223507687558</v>
       </c>
       <c r="E7" t="n">
-        <v>7.882998483200354</v>
+        <v>8.487638091085726</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479245335626269</v>
+        <v>0.7439021617406963</v>
       </c>
       <c r="G7" t="n">
-        <v>30.69378644131744</v>
+        <v>31.09668463810492</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40452854388084</v>
+        <v>34.21949944007203</v>
       </c>
       <c r="I7" t="n">
-        <v>3.205840753190067</v>
+        <v>4.108658556305078</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674528334766417</v>
+        <v>4.649388510879352</v>
       </c>
       <c r="K7" t="n">
-        <v>16.3767829825337</v>
+        <v>14.66400509412466</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23093110403671</v>
+        <v>42.90868259035203</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89327502444864</v>
+        <v>99.86326416141131</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.51909183299757</v>
+        <v>83.93035076120742</v>
       </c>
       <c r="C8" t="n">
-        <v>43.57093313680109</v>
+        <v>41.52345127565999</v>
       </c>
       <c r="D8" t="n">
-        <v>2.01792589552712</v>
+        <v>1.964318304797588</v>
       </c>
       <c r="E8" t="n">
-        <v>9.707713752345192</v>
+        <v>8.783536068405363</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495276336929317</v>
+        <v>0.7449151054076096</v>
       </c>
       <c r="G8" t="n">
-        <v>31.18915571671879</v>
+        <v>30.08722272294168</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47827114987486</v>
+        <v>34.26609484875004</v>
       </c>
       <c r="I8" t="n">
-        <v>5.691949974257865</v>
+        <v>3.428544302107561</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684547710580822</v>
+        <v>4.655719408797561</v>
       </c>
       <c r="K8" t="n">
-        <v>11.48090816700241</v>
+        <v>16.0696492387926</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75883283111427</v>
+        <v>42.29277008120561</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81067413491778</v>
+        <v>99.8858705956582</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.77100853281861</v>
+        <v>82.2561916358415</v>
       </c>
       <c r="C9" t="n">
-        <v>42.70678830564086</v>
+        <v>40.3820197848124</v>
       </c>
       <c r="D9" t="n">
-        <v>1.939261701165674</v>
+        <v>1.885968656464248</v>
       </c>
       <c r="E9" t="n">
-        <v>10.1212726202722</v>
+        <v>8.90993083817923</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508958779966272</v>
+        <v>0.7457785780274141</v>
       </c>
       <c r="G9" t="n">
-        <v>29.97331830033612</v>
+        <v>28.88715076214393</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54121038784485</v>
+        <v>34.30581458926104</v>
       </c>
       <c r="I9" t="n">
-        <v>4.751950407724222</v>
+        <v>2.860432099094302</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693099237478918</v>
+        <v>4.661116112671338</v>
       </c>
       <c r="K9" t="n">
-        <v>13.22899146718139</v>
+        <v>17.74380836415849</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90611050567057</v>
+        <v>41.77893450930389</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84189027849281</v>
+        <v>99.90476265827479</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.93370522915275</v>
+        <v>86.49492150074821</v>
       </c>
       <c r="C10" t="n">
-        <v>41.60743830828869</v>
+        <v>43.32906416025635</v>
       </c>
       <c r="D10" t="n">
-        <v>1.857383033746107</v>
+        <v>1.888074024906355</v>
       </c>
       <c r="E10" t="n">
-        <v>10.35495706099387</v>
+        <v>10.61300653011368</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520646896332689</v>
+        <v>0.746611115025098</v>
       </c>
       <c r="G10" t="n">
-        <v>28.70779784010178</v>
+        <v>30.12974214046833</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59497572313037</v>
+        <v>35.55445499909023</v>
       </c>
       <c r="I10" t="n">
-        <v>3.96612257133944</v>
+        <v>2.896713222237653</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700404310207929</v>
+        <v>4.666319468906862</v>
       </c>
       <c r="K10" t="n">
-        <v>15.06629477084724</v>
+        <v>13.5050784992518</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19426829842729</v>
+        <v>43.06940790274311</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86800137756322</v>
+        <v>99.90355056225127</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.95954112187134</v>
+        <v>86.35056531831573</v>
       </c>
       <c r="C11" t="n">
-        <v>40.24888887432407</v>
+        <v>43.56793075234225</v>
       </c>
       <c r="D11" t="n">
-        <v>1.770125580347782</v>
+        <v>1.878626930390089</v>
       </c>
       <c r="E11" t="n">
-        <v>10.42007742468345</v>
+        <v>10.98762120335028</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530647578235693</v>
+        <v>0.747321633214206</v>
       </c>
       <c r="G11" t="n">
-        <v>27.35914261568691</v>
+        <v>29.99582274056165</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64097885988419</v>
+        <v>35.6051272867832</v>
       </c>
       <c r="I11" t="n">
-        <v>3.309497147048128</v>
+        <v>2.465285316427531</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706654736397307</v>
+        <v>4.670760207588787</v>
       </c>
       <c r="K11" t="n">
-        <v>17.04045887812867</v>
+        <v>13.64943468168425</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60048217612116</v>
+        <v>42.70053651799576</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8898299285739</v>
+        <v>99.91790195202226</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.88932056151349</v>
+        <v>84.60472337585364</v>
       </c>
       <c r="C12" t="n">
-        <v>38.69184219971832</v>
+        <v>42.20595130344682</v>
       </c>
       <c r="D12" t="n">
-        <v>1.679376512909795</v>
+        <v>1.803567226830186</v>
       </c>
       <c r="E12" t="n">
-        <v>10.34604645344335</v>
+        <v>10.89129379091838</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539215875033851</v>
+        <v>0.7479270149280319</v>
       </c>
       <c r="G12" t="n">
-        <v>25.95652084362673</v>
+        <v>28.79735298239926</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68039302515572</v>
+        <v>35.63396987880768</v>
       </c>
       <c r="I12" t="n">
-        <v>2.761052216978364</v>
+        <v>2.056068638669893</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712009921896156</v>
+        <v>4.674543843300198</v>
       </c>
       <c r="K12" t="n">
-        <v>19.11067943848652</v>
+        <v>15.39527662414636</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10554788548826</v>
+        <v>42.33029192472826</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9080695236931</v>
+        <v>99.93151985232146</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.76391780569558</v>
+        <v>85.66218346305197</v>
       </c>
       <c r="C13" t="n">
-        <v>36.99394211624568</v>
+        <v>43.11710219417203</v>
       </c>
       <c r="D13" t="n">
-        <v>1.586946837705513</v>
+        <v>1.804896545194221</v>
       </c>
       <c r="E13" t="n">
-        <v>10.16047306980196</v>
+        <v>11.49596816389592</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546564296981658</v>
+        <v>0.7484782741775412</v>
       </c>
       <c r="G13" t="n">
-        <v>24.5279235204138</v>
+        <v>29.09953865050496</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71419576611563</v>
+        <v>35.94119447213506</v>
       </c>
       <c r="I13" t="n">
-        <v>2.303119496346983</v>
+        <v>1.89411814353463</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716602685613535</v>
+        <v>4.677989213609631</v>
       </c>
       <c r="K13" t="n">
-        <v>21.23608219430443</v>
+        <v>14.33781653694803</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69327979453384</v>
+        <v>42.48199049845102</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92330410508394</v>
+        <v>99.93690922957109</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.81828295395843</v>
+        <v>83.8358087564105</v>
       </c>
       <c r="C14" t="n">
-        <v>40.70333338819507</v>
+        <v>41.58557889151098</v>
       </c>
       <c r="D14" t="n">
-        <v>1.588818386982502</v>
+        <v>1.728236212685177</v>
       </c>
       <c r="E14" t="n">
-        <v>12.26136244089273</v>
+        <v>11.27093095269108</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555464259235082</v>
+        <v>0.7489483055516832</v>
       </c>
       <c r="G14" t="n">
-        <v>26.14560918803602</v>
+        <v>27.86357844284251</v>
       </c>
       <c r="H14" t="n">
-        <v>36.34389450815453</v>
+        <v>35.96376491887863</v>
       </c>
       <c r="I14" t="n">
-        <v>3.00088684194722</v>
+        <v>1.579423014063405</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722165162021924</v>
+        <v>4.68092690969802</v>
       </c>
       <c r="K14" t="n">
-        <v>15.18171704604155</v>
+        <v>16.1641912435895</v>
       </c>
       <c r="L14" t="n">
-        <v>44.01503783422844</v>
+        <v>42.19761547202354</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90008826846507</v>
+        <v>99.94738560712403</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84.27394312186176</v>
+        <v>82.9979459956981</v>
       </c>
       <c r="C15" t="n">
-        <v>40.62378644889742</v>
+        <v>40.97660037916504</v>
       </c>
       <c r="D15" t="n">
-        <v>1.568746378386631</v>
+        <v>1.69289061882756</v>
       </c>
       <c r="E15" t="n">
-        <v>12.52366356067659</v>
+        <v>11.26257958526341</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562945002426544</v>
+        <v>0.749349246091005</v>
       </c>
       <c r="G15" t="n">
-        <v>25.81530404009318</v>
+        <v>27.29371726308491</v>
       </c>
       <c r="H15" t="n">
-        <v>36.37987897344543</v>
+        <v>35.98301769132731</v>
       </c>
       <c r="I15" t="n">
-        <v>2.503215042500689</v>
+        <v>1.332958803035119</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726840626516588</v>
+        <v>4.68343278806878</v>
       </c>
       <c r="K15" t="n">
-        <v>15.72605687813823</v>
+        <v>17.0020540043019</v>
       </c>
       <c r="L15" t="n">
-        <v>43.56679870513247</v>
+        <v>41.97693742982479</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91664203216813</v>
+        <v>99.95559181329173</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>82.11777972640969</v>
+        <v>80.75981648441847</v>
       </c>
       <c r="C16" t="n">
-        <v>38.85551383984987</v>
+        <v>38.94554036907547</v>
       </c>
       <c r="D16" t="n">
-        <v>1.485246634408208</v>
+        <v>1.599487677562502</v>
       </c>
       <c r="E16" t="n">
-        <v>12.20502927383109</v>
+        <v>10.82640013470682</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569354401308147</v>
+        <v>0.7496929641399973</v>
       </c>
       <c r="G16" t="n">
-        <v>24.44123152730764</v>
+        <v>25.78782347285611</v>
       </c>
       <c r="H16" t="n">
-        <v>36.41070997321211</v>
+        <v>35.99952269577248</v>
       </c>
       <c r="I16" t="n">
-        <v>2.087780376702246</v>
+        <v>1.111308513505575</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73084650081759</v>
+        <v>4.685581025874982</v>
       </c>
       <c r="K16" t="n">
-        <v>17.88222027359029</v>
+        <v>19.24018351558152</v>
       </c>
       <c r="L16" t="n">
-        <v>43.19273213537926</v>
+        <v>41.77724948192536</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93046624881941</v>
+        <v>99.96297336658235</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.65495119433415</v>
+        <v>84.91695841571232</v>
       </c>
       <c r="C17" t="n">
-        <v>39.98308551576611</v>
+        <v>41.68018697495789</v>
       </c>
       <c r="D17" t="n">
-        <v>1.48648299027664</v>
+        <v>1.600276713585469</v>
       </c>
       <c r="E17" t="n">
-        <v>12.93705706734491</v>
+        <v>12.29552732239585</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575655318285498</v>
+        <v>0.7500627917811659</v>
       </c>
       <c r="G17" t="n">
-        <v>24.83526283116846</v>
+        <v>27.05488121148404</v>
       </c>
       <c r="H17" t="n">
-        <v>36.81470496564547</v>
+        <v>37.27161792150058</v>
       </c>
       <c r="I17" t="n">
-        <v>2.08909323414169</v>
+        <v>1.256700006332931</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734784573928434</v>
+        <v>4.687892448632286</v>
       </c>
       <c r="K17" t="n">
-        <v>16.34504880566585</v>
+        <v>15.0830415842877</v>
       </c>
       <c r="L17" t="n">
-        <v>43.60228715630507</v>
+        <v>43.1949020949207</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93042147773704</v>
+        <v>99.95813065416628</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.55709379503729</v>
+        <v>86.38423926457141</v>
       </c>
       <c r="C18" t="n">
-        <v>38.20866285939696</v>
+        <v>42.38416233500428</v>
       </c>
       <c r="D18" t="n">
-        <v>1.408052248428406</v>
+        <v>1.601497053179511</v>
       </c>
       <c r="E18" t="n">
-        <v>12.54482243750125</v>
+        <v>12.8706521600601</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581049466936499</v>
+        <v>0.7506347749357402</v>
       </c>
       <c r="G18" t="n">
-        <v>23.52488921735273</v>
+        <v>27.19369967664559</v>
       </c>
       <c r="H18" t="n">
-        <v>36.84091840630295</v>
+        <v>37.30004052535246</v>
       </c>
       <c r="I18" t="n">
-        <v>1.742150621923007</v>
+        <v>1.976247731049623</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73815591683531</v>
+        <v>4.691467343348376</v>
       </c>
       <c r="K18" t="n">
-        <v>18.44290620496269</v>
+        <v>13.61576073542859</v>
       </c>
       <c r="L18" t="n">
-        <v>43.29040056802531</v>
+        <v>43.93425220184346</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94196963238497</v>
+        <v>99.93417527227633</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.70536875674097</v>
+        <v>83.92346900892269</v>
       </c>
       <c r="C19" t="n">
-        <v>37.62610917583564</v>
+        <v>40.23019226070689</v>
       </c>
       <c r="D19" t="n">
-        <v>1.376878263668279</v>
+        <v>1.507899548078896</v>
       </c>
       <c r="E19" t="n">
-        <v>12.50919321047923</v>
+        <v>12.39310139920489</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585597992043964</v>
+        <v>0.751126099309079</v>
       </c>
       <c r="G19" t="n">
-        <v>23.00405304897618</v>
+        <v>25.60439769252004</v>
       </c>
       <c r="H19" t="n">
-        <v>36.86302244916456</v>
+        <v>37.32445508706551</v>
       </c>
       <c r="I19" t="n">
-        <v>1.452663240220837</v>
+        <v>1.647951062062548</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740998745027476</v>
+        <v>4.694538120681743</v>
       </c>
       <c r="K19" t="n">
-        <v>19.29463124325905</v>
+        <v>16.07653099107731</v>
       </c>
       <c r="L19" t="n">
-        <v>43.03086650807411</v>
+        <v>43.63838097790885</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9516069271688</v>
+        <v>99.94510422969304</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.42214757340527</v>
+        <v>81.23812396592751</v>
       </c>
       <c r="C20" t="n">
-        <v>35.56722192235641</v>
+        <v>37.80006178807086</v>
       </c>
       <c r="D20" t="n">
-        <v>1.292324817224068</v>
+        <v>1.406193758751007</v>
       </c>
       <c r="E20" t="n">
-        <v>11.94287219101505</v>
+        <v>11.78621457278058</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589503136104561</v>
+        <v>0.7515495858028763</v>
       </c>
       <c r="G20" t="n">
-        <v>21.5913849730823</v>
+        <v>23.87741562604176</v>
       </c>
       <c r="H20" t="n">
-        <v>36.88199991321208</v>
+        <v>37.34549869430037</v>
       </c>
       <c r="I20" t="n">
-        <v>1.211175905195965</v>
+        <v>1.374066816982932</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743439460065348</v>
+        <v>4.697184911267977</v>
       </c>
       <c r="K20" t="n">
-        <v>21.57785242659473</v>
+        <v>18.76187603407248</v>
       </c>
       <c r="L20" t="n">
-        <v>42.81457389437607</v>
+        <v>43.39228575946604</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95964824332721</v>
+        <v>99.9542235816094</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.58000457459198</v>
+        <v>78.61802587535658</v>
       </c>
       <c r="C21" t="n">
-        <v>38.69842705138706</v>
+        <v>35.39211806627515</v>
       </c>
       <c r="D21" t="n">
-        <v>1.29324761034948</v>
+        <v>1.307438625270963</v>
       </c>
       <c r="E21" t="n">
-        <v>13.65816099259734</v>
+        <v>11.14941957583154</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594922471263916</v>
+        <v>0.7519146353001365</v>
       </c>
       <c r="G21" t="n">
-        <v>23.01515907036606</v>
+        <v>22.20053621121443</v>
       </c>
       <c r="H21" t="n">
-        <v>38.31669237572572</v>
+        <v>37.3636384894394</v>
       </c>
       <c r="I21" t="n">
-        <v>1.790425733887043</v>
+        <v>1.145611867674261</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746826544539945</v>
+        <v>4.699466470625852</v>
       </c>
       <c r="K21" t="n">
-        <v>16.41999542540805</v>
+        <v>21.38197412464341</v>
       </c>
       <c r="L21" t="n">
-        <v>44.82193925051366</v>
+        <v>43.18773928638746</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94036172730875</v>
+        <v>99.96183147730602</v>
       </c>
     </row>
   </sheetData>
